--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5719DFE0-5CF8-A74F-A012-8CCFB2DEF290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F8731A-F043-5548-A407-33201165CD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="15140" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="26800" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,16 +110,16 @@
     <t>Mod 9: Observational Studies</t>
   </si>
   <si>
-    <t>Mod 10: Survey Sampling</t>
-  </si>
-  <si>
-    <t>Mod 11: Writing Survey Instruments</t>
-  </si>
-  <si>
     <t>Mod 12: Survey Weights</t>
   </si>
   <si>
     <t>Mod 13: Putting it all Together!</t>
+  </si>
+  <si>
+    <t>Mod 10: Writing Survey Instruments</t>
+  </si>
+  <si>
+    <t>Mod 11: Survey Sampling</t>
   </si>
 </sst>
 </file>
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -252,6 +252,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -846,8 +849,8 @@
         <f>C20+2</f>
         <v>46324</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>25</v>
+      <c r="D21" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="F21" s="7"/>
     </row>
@@ -862,8 +865,8 @@
         <f>C21+5</f>
         <v>46329</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>25</v>
+      <c r="D22" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -879,8 +882,8 @@
         <f>C22+2</f>
         <v>46331</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>25</v>
+      <c r="D23" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -896,7 +899,7 @@
         <v>46336</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3"/>
     </row>
@@ -912,7 +915,7 @@
         <v>46338</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3"/>
     </row>
@@ -928,7 +931,7 @@
         <v>46343</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -944,7 +947,7 @@
         <v>46345</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H27" s="1"/>
     </row>
@@ -989,7 +992,7 @@
         <v>46357</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F30" s="5"/>
       <c r="H30" s="1"/>
@@ -1006,7 +1009,7 @@
         <v>46359</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F31" s="4"/>
       <c r="H31" s="1"/>
@@ -1023,7 +1026,7 @@
         <v>46364</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H32" s="1"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F8731A-F043-5548-A407-33201165CD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CB05E7-F716-D94A-9D5E-97FF0C9D4E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="26800" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="10900" windowWidth="26800" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
   <si>
     <t>week</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Mod 11: Survey Sampling</t>
+  </si>
+  <si>
+    <t>1-prep/1.1-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -524,6 +527,9 @@
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
+      <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CB05E7-F716-D94A-9D5E-97FF0C9D4E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13940E2D-E759-EE4D-B3E5-5B98E9ECDF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10900" windowWidth="26800" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
   <si>
     <t>week</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>1-prep/1.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/1.2-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -545,6 +548,9 @@
       <c r="D3" s="8" t="s">
         <v>16</v>
       </c>
+      <c r="E3" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13940E2D-E759-EE4D-B3E5-5B98E9ECDF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A0768-222F-6343-8113-8C0F3745C36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
   <si>
     <t>week</t>
   </si>
@@ -41,9 +41,6 @@
     <t>topic</t>
   </si>
   <si>
-    <t>slides</t>
-  </si>
-  <si>
     <t>activity</t>
   </si>
   <si>
@@ -122,10 +119,22 @@
     <t>Mod 11: Survey Sampling</t>
   </si>
   <si>
-    <t>1-prep/1.1-prep.qmd</t>
-  </si>
-  <si>
-    <t>1-prep/1.2-prep.qmd</t>
+    <t>class_slides</t>
+  </si>
+  <si>
+    <t>prep_slides</t>
+  </si>
+  <si>
+    <t>2-slides/01.1-basics-of-doe.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/01.2-controlling-for-variability.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/01.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/01.2-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -481,605 +490,628 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="31.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.33203125" customWidth="1"/>
-    <col min="8" max="8" width="27.5" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.33203125" customWidth="1"/>
+    <col min="9" max="9" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6">
         <v>46259</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6">
         <f>C2+2</f>
         <v>46261</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6">
         <f>C2+7</f>
         <v>46266</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6">
         <f>C4+2</f>
         <v>46268</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6">
         <f>C4+7</f>
         <v>46273</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6">
         <f>C6+2</f>
         <v>46275</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="6">
         <f>C6+7</f>
         <v>46280</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6">
         <f>C8+2</f>
         <v>46282</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="6">
         <f>C8+7</f>
         <v>46287</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6">
         <f>C10+2</f>
         <v>46289</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6">
         <f>C10+7</f>
         <v>46294</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
         <f>C12+2</f>
         <v>46296</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="6">
         <f>C12+7</f>
         <v>46301</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="6">
         <f>C14+2</f>
         <v>46303</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
         <f>C14+7</f>
         <v>46308</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6">
         <f>C16+2</f>
         <v>46310</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="6">
         <f>C16+7</f>
         <v>46315</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" s="6">
         <f>C18+2</f>
         <v>46317</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6">
         <f>C19+5</f>
         <v>46322</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="6">
         <f>C20+2</f>
         <v>46324</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="6">
         <f>C21+5</f>
         <v>46329</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="6">
         <f>C22+2</f>
         <v>46331</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6">
         <f>C23+5</f>
         <v>46336</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>12</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6">
         <f>C24+2</f>
         <v>46338</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="6">
         <f>C25+5</f>
         <v>46343</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="6">
         <f>C26+2</f>
         <v>46345</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="6">
         <f>C27+5</f>
         <v>46350</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="6">
         <f>C28+2</f>
         <v>46352</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="6">
         <f>C29+5</f>
         <v>46357</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="6">
         <f>C30+2</f>
         <v>46359</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>15</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="6">
         <f>C31+5</f>
         <v>46364</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>15</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="6">
         <f>C32+2</f>
         <v>46366</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6"/>
-      <c r="F35" s="4"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F36" s="4"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F37" s="1"/>
-    </row>
-    <row r="39" spans="1:8" ht="13" x14ac:dyDescent="0.15">
-      <c r="F39" s="2"/>
+      <c r="G35" s="4"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G36" s="4"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="39" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" ht="13" x14ac:dyDescent="0.15">
-      <c r="F40" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="G40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A0768-222F-6343-8113-8C0F3745C36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D804B136-D75D-B04B-86E4-BE536ED31DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>week</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>1-prep/01.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/01.1-activity-turkey-in-pens.qmd</t>
   </si>
 </sst>
 </file>
@@ -548,6 +551,9 @@
       <c r="F2" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="H2" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D804B136-D75D-B04B-86E4-BE536ED31DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEB8A50-9FE2-A049-A6A0-ADDF9FCC27E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>week</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>3-activities/instructions/01.1-activity-turkey-in-pens.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1huFMgeDgVDLGn2SQCMUyEFC3V7_B0oH9zRA3VXeGsgk/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -551,6 +554,9 @@
       <c r="F2" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
       <c r="H2" s="7" t="s">
         <v>34</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEB8A50-9FE2-A049-A6A0-ADDF9FCC27E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B27ACEF-160E-D647-9EB1-A6AD12888D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
   <si>
     <t>week</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1huFMgeDgVDLGn2SQCMUyEFC3V7_B0oH9zRA3VXeGsgk/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/01.2-activity-sources-of-variation.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1i0n-4905RxE9mdDFWk7eq4qvKPRdyUzQVsWy-UYQXWQ/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -581,6 +587,12 @@
       <c r="F3" s="7" t="s">
         <v>31</v>
       </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B27ACEF-160E-D647-9EB1-A6AD12888D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56471DE9-5700-5C4F-B700-6DB8A4A7A7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="39">
   <si>
     <t>week</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1i0n-4905RxE9mdDFWk7eq4qvKPRdyUzQVsWy-UYQXWQ/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>4-labs/lab1-recruit.qmd</t>
   </si>
 </sst>
 </file>
@@ -593,6 +596,9 @@
       <c r="H3" s="7" t="s">
         <v>36</v>
       </c>
+      <c r="I3" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56471DE9-5700-5C4F-B700-6DB8A4A7A7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EC4C3A-56F5-3145-A012-DD893FE880FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
   <si>
     <t>week</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>4-labs/lab1-recruit.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/02.1-crd-design-analysis-model.qmd</t>
   </si>
 </sst>
 </file>
@@ -614,6 +617,12 @@
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EC4C3A-56F5-3145-A012-DD893FE880FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD24B65A-3E77-1840-ADD3-ED0C51FBFF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
   <si>
     <t>week</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>2-slides/02.1-crd-design-analysis-model.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/02.1-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -618,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>39</v>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD24B65A-3E77-1840-ADD3-ED0C51FBFF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66012BE-7A47-6F41-958E-B5E9A770702F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24680" yWindow="-20040" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>week</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>1-prep/02.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/02.1-activity-intro-to-crd.qmd</t>
   </si>
 </sst>
 </file>
@@ -626,6 +629,9 @@
       <c r="F4" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="H4" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66012BE-7A47-6F41-958E-B5E9A770702F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9B7577-F227-974E-BD01-0EB8EBC4B728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24680" yWindow="-20040" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
   <si>
     <t>week</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>3-activities/instructions/02.1-activity-intro-to-crd.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/02.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1TPYCM47Z3NjaMAICOFkSf6Bc7VC0w9rspReTiJoYckM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>2-slides/02.2-crd-contrasts.qmd</t>
   </si>
 </sst>
 </file>
@@ -629,6 +638,9 @@
       <c r="F4" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
       <c r="H4" s="7" t="s">
         <v>41</v>
       </c>
@@ -646,6 +658,12 @@
       </c>
       <c r="D5" s="8" t="s">
         <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="I5" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9B7577-F227-974E-BD01-0EB8EBC4B728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF93EC-3A64-6E4F-9179-816731A7F390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>week</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>2-slides/02.2-crd-contrasts.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/02.2-activity-comparing-means.qmd</t>
   </si>
 </sst>
 </file>
@@ -665,6 +668,9 @@
       <c r="F5" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="H5" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF93EC-3A64-6E4F-9179-816731A7F390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCA9628-625C-1142-B2D1-B273A8CA5B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>week</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>3-activities/instructions/02.2-activity-comparing-means.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1Ek6Zr9Vd8tYFCtOpWvfTYQTOjVFxCXzuQgJyph8KDSE/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -668,6 +671,9 @@
       <c r="F5" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
       <c r="H5" s="7" t="s">
         <v>45</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCA9628-625C-1142-B2D1-B273A8CA5B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D7EDB3-593D-3C4A-BFA3-293AAB99DE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
   <si>
     <t>week</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1Ek6Zr9Vd8tYFCtOpWvfTYQTOjVFxCXzuQgJyph8KDSE/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>1-prep/03.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/03.1-power.qmd</t>
   </si>
 </sst>
 </file>
@@ -693,8 +699,12 @@
       <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D7EDB3-593D-3C4A-BFA3-293AAB99DE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B178CA-9A72-1445-AE23-ED785E8811A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>week</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>2-slides/03.1-power.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1LECCxIsoXrOlfq4hSeCm90mX3H_KjaeMtiUCJn4d890/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/03.1-activity-what-impacts-power.qmd</t>
   </si>
 </sst>
 </file>
@@ -705,8 +711,12 @@
       <c r="F6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B178CA-9A72-1445-AE23-ED785E8811A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3B4158-EB21-A142-A0B0-434A7C76D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
   <si>
     <t>week</t>
   </si>
@@ -186,6 +186,15 @@
   </si>
   <si>
     <t>3-activities/instructions/03.1-activity-what-impacts-power.qmd</t>
+  </si>
+  <si>
+    <t>4-labs/lab2-crd.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/04.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/04.1-factorials.qmd</t>
   </si>
 </sst>
 </file>
@@ -717,6 +726,9 @@
       <c r="H6" s="7" t="s">
         <v>50</v>
       </c>
+      <c r="I6" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
@@ -732,8 +744,12 @@
       <c r="D7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="7"/>
       <c r="I7" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3B4158-EB21-A142-A0B0-434A7C76D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E1E834-AD77-EF49-A8C3-A968C721B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
   <si>
     <t>week</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>2-slides/04.1-factorials.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/04.1-activity-contrasts-for-factorials.qmd</t>
   </si>
 </sst>
 </file>
@@ -751,6 +754,9 @@
         <v>53</v>
       </c>
       <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E1E834-AD77-EF49-A8C3-A968C721B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F1A6C-AF7A-F248-9522-52E54B4958BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="56">
   <si>
     <t>week</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>3-activities/instructions/04.1-activity-contrasts-for-factorials.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/12ID6VbCZhW5Nx4u54auJqxmrAmgb7ZwLVz-DfXAOtcE/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -753,7 +756,9 @@
       <c r="F7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H7" s="7" t="s">
         <v>54</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F1A6C-AF7A-F248-9522-52E54B4958BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A20FA6D-7810-A947-93C3-BBFD31C62842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
   <si>
     <t>week</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/12ID6VbCZhW5Nx4u54auJqxmrAmgb7ZwLVz-DfXAOtcE/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>6-exams/practice/midterm1-practice.qmd</t>
   </si>
 </sst>
 </file>
@@ -797,7 +800,9 @@
       <c r="D9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="I9" s="7"/>
